--- a/akreditasi/docs/tabel_xlsx/LKPS/LKPS-Tabel 4.C.2 - Diseminasi Hasil PkM No Nama DTPR (Ketua) Judul Diseminasi.xlsx
+++ b/akreditasi/docs/tabel_xlsx/LKPS/LKPS-Tabel 4.C.2 - Diseminasi Hasil PkM No Nama DTPR (Ketua) Judul Diseminasi.xlsx
@@ -26,34 +26,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,22 +56,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,182 +450,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="11.45" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12.5" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12.5" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dokumen</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>LKPS — Laporan Kinerja Program Studi</t>
-        </is>
-      </c>
+          <t>Tabel 4.C.2 Diseminasi Hasil PkM No Nama DTPR (Ketua) Judul Diseminasi Hasil PkM (L/N/I) TS- 2 TS- 1 TS Link Bukti Ciri kh</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Nomor tabel</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>4.C.2</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Judul</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Nama tabel</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Diseminasi Hasil PkM No Nama DTPR (Ketua) Judul Diseminasi Hasil PkM (L/N/I) TS- 2 TS- 1 TS Link Bukti Ciri kh</t>
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Diseminasi</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Ciri</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Halaman PDF</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>95</v>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Nama DTPR</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TS-</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>TS-</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Halaman PDF</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>95</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Hasil PkM</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Link Bukti</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>khas</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah kolom</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Header tabel</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Nama DTPR</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Judul</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Diseminasi Hasil PkM</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>TS-</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>TS-</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Link Bukti</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Ciri khas</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Catatan</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Nomor dan judul dari caption bernomor di badan LKPS; header kolom digabung dari baris header bertingkat blok tabel di bawah caption.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="D3:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>